--- a/data/trans_orig/P57B4_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B4_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha tenido la sensación de disfrutar de la vida en 2023</t>
+          <t>Población según si ha tenido la sensación de disfrutar de la vida en 2023 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>15434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50240</t>
+          <t>53857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59285</t>
+          <t>60141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232831</t>
+          <t>230384</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268342</t>
+          <t>268076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228626</t>
+          <t>228593</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248048</t>
+          <t>248568</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>466434</t>
+          <t>468747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510795</t>
+          <t>510679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19546</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>40394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36702</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54854</t>
+          <t>55023</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60862</t>
+          <t>60252</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89816</t>
+          <t>88374</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1799</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>538</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2718</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>270970</t>
+          <t>266438</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>327435</t>
+          <t>325544</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>207798</t>
+          <t>205575</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247872</t>
+          <t>245845</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>490634</t>
+          <t>488410</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>561841</t>
+          <t>562654</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156916</t>
+          <t>159830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>212708</t>
+          <t>213785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>223575</t>
+          <t>225649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>264565</t>
+          <t>266250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>393602</t>
+          <t>391524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>463550</t>
+          <t>466192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>18833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48994</t>
+          <t>48789</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>17976</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32799</t>
+          <t>33273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42288</t>
+          <t>41922</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76124</t>
+          <t>73451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>26082</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29819</t>
+          <t>29254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135745</t>
+          <t>138052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171713</t>
+          <t>173522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114169</t>
+          <t>117256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146447</t>
+          <t>147518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262012</t>
+          <t>260561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309249</t>
+          <t>310183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85730</t>
+          <t>85621</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>119119</t>
+          <t>117792</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>114353</t>
+          <t>116087</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>147306</t>
+          <t>145492</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>208076</t>
+          <t>211419</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>255492</t>
+          <t>256947</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34499</t>
+          <t>34771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57016</t>
+          <t>58582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52935</t>
+          <t>52508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74104</t>
+          <t>75467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93658</t>
+          <t>92280</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124017</t>
+          <t>124457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>19567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>26735</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23711</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>41845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>165519</t>
+          <t>166680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>207347</t>
+          <t>207290</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>109158</t>
+          <t>116169</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>236136</t>
+          <t>236211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>261138</t>
+          <t>265699</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>431353</t>
+          <t>431690</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66285</t>
+          <t>67203</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103012</t>
+          <t>102134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>160224</t>
+          <t>164940</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>316172</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>242408</t>
+          <t>238833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>445582</t>
+          <t>433943</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,03%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20778</t>
+          <t>18787</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50701</t>
+          <t>49371</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41369</t>
+          <t>40983</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>76285</t>
+          <t>75428</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19734</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>34455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39233</t>
+          <t>37995</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>27281</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>35113</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59164</t>
+          <t>59423</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>89751</t>
+          <t>89851</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>113063</t>
+          <t>111400</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>94611</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115031</t>
+          <t>114565</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>190807</t>
+          <t>192028</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>221336</t>
+          <t>220580</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57876</t>
+          <t>58035</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71084</t>
+          <t>71524</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91056</t>
+          <t>91209</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115479</t>
+          <t>115188</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>142481</t>
+          <t>143051</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105713</t>
+          <t>106530</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>136629</t>
+          <t>137588</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106230</t>
+          <t>106282</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>132299</t>
+          <t>132128</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>220662</t>
+          <t>219202</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>260943</t>
+          <t>261091</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>82481</t>
+          <t>81937</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109893</t>
+          <t>109597</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>71570</t>
+          <t>73244</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>95846</t>
+          <t>95711</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>162361</t>
+          <t>160697</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>199267</t>
+          <t>198104</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30981</t>
+          <t>29613</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50462</t>
+          <t>50218</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>34313</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>51006</t>
+          <t>52623</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68433</t>
+          <t>69252</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>96048</t>
+          <t>97360</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19649</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>17113</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>32503</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>245721</t>
+          <t>246002</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>307509</t>
+          <t>305546</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>308283</t>
+          <t>308977</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>688118</t>
+          <t>642534</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>587696</t>
+          <t>589893</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1037971</t>
+          <t>1006989</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>224357</t>
+          <t>224088</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>282585</t>
+          <t>280632</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>116982</t>
+          <t>150718</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>399570</t>
+          <t>399083</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>317222</t>
+          <t>340822</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>646894</t>
+          <t>650060</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>54916</t>
+          <t>54344</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>90036</t>
+          <t>91382</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>32622</t>
+          <t>39502</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>109380</t>
+          <t>110080</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>87612</t>
+          <t>91549</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>183906</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>61461</t>
+          <t>57492</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>44439</t>
+          <t>43320</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>85044</t>
+          <t>83722</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>379743</t>
+          <t>379635</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>750961</t>
+          <t>748639</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>238969</t>
+          <t>236032</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>283640</t>
+          <t>281257</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>629709</t>
+          <t>630024</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1101373</t>
+          <t>1121951</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>127892</t>
+          <t>126576</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>395720</t>
+          <t>392833</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>281760</t>
+          <t>281837</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>326330</t>
+          <t>326495</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>374670</t>
+          <t>353526</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>700279</t>
+          <t>701097</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>43398</t>
+          <t>43293</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>142494</t>
+          <t>143816</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>123581</t>
+          <t>124094</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>161707</t>
+          <t>160227</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>153514</t>
+          <t>146903</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>290497</t>
+          <t>293853</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>24628</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>21137</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>39912</t>
+          <t>40626</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1468868</t>
+          <t>1460564</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2056842</t>
+          <t>1982501</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1228477</t>
+          <t>1228341</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1847207</t>
+          <t>1774694</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2753967</t>
+          <t>2735154</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3622464</t>
+          <t>3545440</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1029513</t>
+          <t>1090708</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1477263</t>
+          <t>1486636</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1315468</t>
+          <t>1338771</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1766227</t>
+          <t>1768763</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2545387</t>
+          <t>2601003</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3189077</t>
+          <t>3199985</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>296750</t>
+          <t>304242</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>432869</t>
+          <t>431791</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>413900</t>
+          <t>422031</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>562106</t>
+          <t>563810</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>766629</t>
+          <t>773080</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>964875</t>
+          <t>972187</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>57405</t>
+          <t>57652</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>108991</t>
+          <t>109672</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>85539</t>
+          <t>85084</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>125495</t>
+          <t>127549</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>153767</t>
+          <t>155875</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>218549</t>
+          <t>224266</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B4_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B4_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28142</t>
+          <t>24559</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>15356</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53857</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33113</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20719</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60141</t>
+          <t>45066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>253398</t>
+          <t>260800</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>230384</t>
+          <t>243002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268076</t>
+          <t>272960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>238970</t>
+          <t>259594</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228593</t>
+          <t>249250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248568</t>
+          <t>269602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>492368</t>
+          <t>520395</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>468747</t>
+          <t>500886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510679</t>
+          <t>537244</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28621</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19582</t>
+          <t>24054</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40394</t>
+          <t>43654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45157</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36768</t>
+          <t>41123</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55023</t>
+          <t>60517</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>73778</t>
+          <t>82948</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>69242</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88374</t>
+          <t>97069</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>487</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>487</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>298648</t>
+          <t>301151</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>266438</t>
+          <t>270572</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>325544</t>
+          <t>328920</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>226446</t>
+          <t>241462</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>205575</t>
+          <t>221998</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>245845</t>
+          <t>263756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>525093</t>
+          <t>542613</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>488410</t>
+          <t>505928</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>562654</t>
+          <t>581244</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>184576</t>
+          <t>192914</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159830</t>
+          <t>164301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213785</t>
+          <t>220853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>244499</t>
+          <t>260780</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225649</t>
+          <t>237574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>266250</t>
+          <t>281515</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>429075</t>
+          <t>453694</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391524</t>
+          <t>418090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>466192</t>
+          <t>490606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>32338</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>20259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48789</t>
+          <t>49758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33273</t>
+          <t>33751</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>55976</t>
+          <t>57425</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41922</t>
+          <t>42713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73451</t>
+          <t>77730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>16649</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10517</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20802</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14212</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29254</t>
+          <t>30360</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>512556</t>
+          <t>543978</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>512556</t>
+          <t>543978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>512556</t>
+          <t>543978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1030946</t>
+          <t>1074625</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1030946</t>
+          <t>1074625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1030946</t>
+          <t>1074625</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>154657</t>
+          <t>154105</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>138052</t>
+          <t>136930</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173522</t>
+          <t>171644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>131462</t>
+          <t>132380</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117256</t>
+          <t>117774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147518</t>
+          <t>147381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>286119</t>
+          <t>286485</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260561</t>
+          <t>263085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>307069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>101610</t>
+          <t>100260</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85621</t>
+          <t>86073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>117792</t>
+          <t>118378</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>130074</t>
+          <t>131935</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>116087</t>
+          <t>117988</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>145492</t>
+          <t>148004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>231684</t>
+          <t>232195</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>211419</t>
+          <t>210863</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>256947</t>
+          <t>255477</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44961</t>
+          <t>46406</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34771</t>
+          <t>36102</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58582</t>
+          <t>59440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62899</t>
+          <t>67009</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52508</t>
+          <t>55751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75467</t>
+          <t>78060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>113414</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92280</t>
+          <t>97805</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124457</t>
+          <t>130843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>20484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>27020</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>32204</t>
+          <t>32834</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24132</t>
+          <t>24479</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41845</t>
+          <t>42452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>313857</t>
+          <t>313950</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>313857</t>
+          <t>313950</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>313857</t>
+          <t>313950</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>344010</t>
+          <t>350979</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>344010</t>
+          <t>350979</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>344010</t>
+          <t>350979</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>657867</t>
+          <t>664928</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>657867</t>
+          <t>664928</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>657867</t>
+          <t>664928</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>186573</t>
+          <t>220477</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>166680</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>207290</t>
+          <t>242185</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>185039</t>
+          <t>212232</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>116169</t>
+          <t>192911</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>236211</t>
+          <t>231830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>371613</t>
+          <t>432708</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>265699</t>
+          <t>400797</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>431690</t>
+          <t>464068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>61,0%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>84671</t>
+          <t>101766</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67203</t>
+          <t>83200</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102134</t>
+          <t>124620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>224657</t>
+          <t>138185</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>164940</t>
+          <t>120348</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>313037</t>
+          <t>156717</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>309329</t>
+          <t>239950</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238833</t>
+          <t>214950</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>433943</t>
+          <t>267760</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>25325</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>41788</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35129</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18787</t>
+          <t>28931</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49371</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>58143</t>
+          <t>63553</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>40983</t>
+          <t>49875</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>75428</t>
+          <t>80868</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -2771,102 +2771,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>12914</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>7922</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>21196</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>24554</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>16561</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>36089</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>3,23%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>12019</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>6463</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>19734</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>21854</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>14201</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>34455</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>304094</t>
+          <t>359208</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>304094</t>
+          <t>359208</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>304094</t>
+          <t>359208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>456844</t>
+          <t>401559</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>456844</t>
+          <t>401559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>456844</t>
+          <t>401559</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>760939</t>
+          <t>760766</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>760939</t>
+          <t>760766</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>760939</t>
+          <t>760766</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>22089</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37995</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>15545</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>31870</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>46623</t>
+          <t>54024</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35113</t>
+          <t>42104</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59423</t>
+          <t>70111</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>101391</t>
+          <t>116597</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>89851</t>
+          <t>103429</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111400</t>
+          <t>128705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>104900</t>
+          <t>115898</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>94708</t>
+          <t>104526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114565</t>
+          <t>126952</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>206291</t>
+          <t>232496</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>192028</t>
+          <t>214499</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>220580</t>
+          <t>248930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,82%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>47708</t>
+          <t>54496</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>44659</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58035</t>
+          <t>65632</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>80691</t>
+          <t>85534</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71524</t>
+          <t>76180</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91209</t>
+          <t>96752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>128399</t>
+          <t>140030</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115188</t>
+          <t>124630</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>143051</t>
+          <t>154184</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>177593</t>
+          <t>204547</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>177593</t>
+          <t>204547</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>177593</t>
+          <t>204547</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>207461</t>
+          <t>226002</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207461</t>
+          <t>226002</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207461</t>
+          <t>226002</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>385054</t>
+          <t>430549</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>385054</t>
+          <t>430549</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>385054</t>
+          <t>430549</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>121048</t>
+          <t>117110</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>106530</t>
+          <t>102327</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>137588</t>
+          <t>131889</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>119481</t>
+          <t>121066</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106282</t>
+          <t>107632</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>132128</t>
+          <t>133720</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>240529</t>
+          <t>238176</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>219202</t>
+          <t>218256</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>261091</t>
+          <t>257923</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>96423</t>
+          <t>98846</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>81937</t>
+          <t>85592</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109597</t>
+          <t>113676</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>83432</t>
+          <t>85547</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>73244</t>
+          <t>74036</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>95711</t>
+          <t>98700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>179856</t>
+          <t>184394</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>160697</t>
+          <t>165717</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>198104</t>
+          <t>203800</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>39654</t>
+          <t>40862</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29613</t>
+          <t>32148</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50218</t>
+          <t>51256</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>42291</t>
+          <t>44643</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34313</t>
+          <t>36268</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52623</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>81945</t>
+          <t>85505</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>69252</t>
+          <t>72284</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>97360</t>
+          <t>99695</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17328</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>26382</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>277690</t>
+          <t>322501</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>246002</t>
+          <t>294247</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>305546</t>
+          <t>351521</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>446273</t>
+          <t>295567</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>308977</t>
+          <t>269329</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>642534</t>
+          <t>320597</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>723963</t>
+          <t>618068</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>589893</t>
+          <t>578427</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1006989</t>
+          <t>657683</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>250733</t>
+          <t>297552</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>224088</t>
+          <t>266451</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>280632</t>
+          <t>326530</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>295335</t>
+          <t>346356</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>150718</t>
+          <t>321173</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>399083</t>
+          <t>373104</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>546068</t>
+          <t>643908</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>340822</t>
+          <t>606702</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>650060</t>
+          <t>688591</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>70621</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>54344</t>
+          <t>60982</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>91382</t>
+          <t>100081</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>77558</t>
+          <t>95238</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>39502</t>
+          <t>77940</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>110080</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>148179</t>
+          <t>174623</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>91549</t>
+          <t>150435</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>183906</t>
+          <t>203342</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>23444</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>57492</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>29252</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>43320</t>
+          <t>44943</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>52697</t>
+          <t>51466</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>83722</t>
+          <t>67406</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>622488</t>
+          <t>717779</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>622488</t>
+          <t>717779</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>622488</t>
+          <t>717779</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>848419</t>
+          <t>770286</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>848419</t>
+          <t>770286</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>848419</t>
+          <t>770286</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1470907</t>
+          <t>1488065</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1470907</t>
+          <t>1488065</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1470907</t>
+          <t>1488065</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>533202</t>
+          <t>340948</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>379635</t>
+          <t>311281</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>748639</t>
+          <t>373130</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>259129</t>
+          <t>301852</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>236032</t>
+          <t>275474</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>281257</t>
+          <t>329471</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>792332</t>
+          <t>642799</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>630024</t>
+          <t>603702</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1121951</t>
+          <t>684950</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>282104</t>
+          <t>325724</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>126576</t>
+          <t>296181</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>392833</t>
+          <t>355039</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>304481</t>
+          <t>355616</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>281837</t>
+          <t>330198</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>326495</t>
+          <t>381375</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>586585</t>
+          <t>681341</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>353526</t>
+          <t>643322</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>701097</t>
+          <t>724770</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>99045</t>
+          <t>114934</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>43293</t>
+          <t>97412</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>143816</t>
+          <t>135448</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>140105</t>
+          <t>156240</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>124094</t>
+          <t>137684</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>160227</t>
+          <t>177575</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>239150</t>
+          <t>271175</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>146903</t>
+          <t>245482</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>293853</t>
+          <t>301592</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>24628</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>14016</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>27016</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>28386</t>
+          <t>34089</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>23885</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>47363</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1627288</t>
+          <t>1513044</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1460564</t>
+          <t>1446631</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1982501</t>
+          <t>1583281</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1392096</t>
+          <t>1331827</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1228341</t>
+          <t>1278789</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1774694</t>
+          <t>1383064</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>3019384</t>
+          <t>2844872</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2735154</t>
+          <t>2763340</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3545440</t>
+          <t>2936468</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1354907</t>
+          <t>1494460</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1090708</t>
+          <t>1428390</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1486636</t>
+          <t>1556661</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1626348</t>
+          <t>1693913</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1338771</t>
+          <t>1641064</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1768763</t>
+          <t>1742774</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2981254</t>
+          <t>3188373</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2601003</t>
+          <t>3100265</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3199985</t>
+          <t>3268935</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>384778</t>
+          <t>426154</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>304242</t>
+          <t>386282</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>431791</t>
+          <t>465187</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>508651</t>
+          <t>562520</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>422031</t>
+          <t>526464</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>563810</t>
+          <t>597818</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>893429</t>
+          <t>988673</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>773080</t>
+          <t>931602</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>972187</t>
+          <t>1042631</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>79019</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>57652</t>
+          <t>62133</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>109672</t>
+          <t>97436</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>106617</t>
+          <t>115686</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>85084</t>
+          <t>97730</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>127549</t>
+          <t>132065</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>184584</t>
+          <t>194705</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>155875</t>
+          <t>173174</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>224266</t>
+          <t>222563</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3444939</t>
+          <t>3512677</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3444939</t>
+          <t>3512677</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3444939</t>
+          <t>3512677</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3633712</t>
+          <t>3703946</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3633712</t>
+          <t>3703946</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3633712</t>
+          <t>3703946</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7078651</t>
+          <t>7216623</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7078651</t>
+          <t>7216623</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7078651</t>
+          <t>7216623</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
